--- a/stories/arbres/ATOM-EMO.LEX.009-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Iris est dans le salon avec maman. Tom tient le grand puzzle. Iris le regarde. Son ventre se serre. Elle dit : je suis jalouse. Jaloux, c'est cette envie. Maman écoute. Iris va près de Tom. Elle dit : je voudrais demander un tour. Tom dit : encore deux pièces. Iris attend. Les mains restent sur ses genoux. Puis Tom passe une pièce. Iris a son tour. Maman dit : tu as demandé un tour. Tu as attendu.</t>
+          <t>Iris est dans le salon avec maman. Tom tient le grand puzzle. Iris le regarde. Son ventre se serre. Je suis jalouse. Jaloux, c'est cette envie. Maman écoute. Iris va près de Tom. Je voudrais demander un tour. Encore deux pièces. Iris attend. Les mains restent sur ses genoux. Puis Tom passe une pièce. Iris a son tour. Tu as demandé un tour. Tu as attendu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Iris est dans le salon avec maman. Tom tient le grand puzzle. Iris le regarde. Son ventre se serre.
+narrateur|Je suis jalouse. Jaloux, c'est cette envie. Maman écoute.
+narrateur|Iris va près de Tom.
+narrateur|Je voudrais demander un tour.
+copain|Encore deux pièces.
+narrateur|Iris attend. Les mains restent sur ses genoux. Puis Tom passe une pièce. Iris a son tour.
+maman|Tu as demandé un tour. Tu as attendu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1467,6 +1494,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Iris veut le puzzle. Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1491,7 +1523,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Iris a dit : je suis jalouse. Elle a demandé un tour.</t>
+          <t>Iris Je suis jalouse. Elle a demandé un tour.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1629,6 +1661,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Iris
+enfant-f|Je suis jalouse. Elle a demandé un tour.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1825,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range la boîte. Iris pose une dernière pièce.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1992,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2032,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 maman|Tu as demandé un tour. Tu as attendu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Iris veut le puzzle. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
 enfant-f|Je suis jalouse. Elle a demandé un tour.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1830,6 +1838,7 @@
           <t>narrateur|Maman range la boîte. Iris pose une dernière pièce.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1997,6 +2006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2015,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2049,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2264,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.009-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Iris est jalouse du puzzle</t>
+          <t>Le puzzle de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël a le grand puzzle. Mila dit qu'elle est jalouse. Elle demande un tour. Elle attend.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Iris est dans le salon avec maman. Tom tient le grand puzzle. Iris le regarde. Son ventre se serre. Je suis jalouse. Jaloux, c'est cette envie. Maman écoute. Iris va près de Tom. Je voudrais demander un tour. Encore deux pièces. Iris attend. Les mains restent sur ses genoux. Puis Tom passe une pièce. Iris a son tour. Tu as demandé un tour. Tu as attendu.</t>
+          <t>Le rideau laisse un rayon jaune. Le rayon tombe sur le tapis. Le tapis a des étoiles grises. Un couvercle de boîte est penché. Il s'appuie contre le canapé. Les pièces du puzzle sont dans un plateau. Le bois du plateau est tiède. Une chaussette attend sur le bras du canapé. Ça sent le linge propre, un peu. Je plie le linge, Mila. Raphaël a déjà commencé le puzzle. Le rayon est chaud, maman. Oui. Il caresse le tapis. Les étoiles du tapis brillent un peu. En ce moment, Raphaël tient le grand puzzle. Une pièce verte est entre ses doigts. Mila le regarde. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jalouse. Je t'écoute. Jaloux, c'est cette envie. On peut le dire. Mila va près de Raphaël. Je voudrais demander un tour. Encore deux pièces. On attend la réponse. Mila attend. Les mains restent sur ses genoux. Elle compte tout bas. Une pièce. Encore une pièce. Raphaël pose une pièce. Puis une autre. Le vert rejoint le vert. C'est ton tour. Raphaël passe une pièce. Mila a son tour. Merci, Raphaël. Tu as demandé un tour. Tu as attendu. Bravo, Mila. Tu as fait du bon travail. J'ai dit : je suis jalouse. Puis tu as demandé. Le rayon a un peu bougé. Il touche maintenant une étoile du tapis.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,52 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Iris est dans le salon avec maman. Tom tient le grand puzzle. Iris le regarde. Son ventre se serre.
-narrateur|Je suis jalouse. Jaloux, c'est cette envie. Maman écoute.
-narrateur|Iris va près de Tom.
-narrateur|Je voudrais demander un tour.
-copain|Encore deux pièces.
-narrateur|Iris attend. Les mains restent sur ses genoux. Puis Tom passe une pièce. Iris a son tour.
-maman|Tu as demandé un tour. Tu as attendu.</t>
+          <t>narrateur|Le rideau laisse un rayon jaune.
+narrateur|Le rayon tombe sur le tapis.
+narrateur|Le tapis a des étoiles grises.
+narrateur|Un couvercle de boîte est penché.
+narrateur|Il s'appuie contre le canapé.
+narrateur|Les pièces du puzzle sont dans un plateau.
+narrateur|Le bois du plateau est tiède.
+narrateur|Une chaussette attend sur le bras du canapé.
+narrateur|Ça sent le linge propre, un peu.
+maman|Je plie le linge, Mila.
+papa|Raphaël a déjà commencé le puzzle.
+enfant-f|Le rayon est chaud, maman.
+maman|Oui. Il caresse le tapis.
+papa|Les étoiles du tapis brillent un peu.
+narrateur|En ce moment, Raphaël tient le grand puzzle.
+narrateur|Une pièce verte est entre ses doigts.
+narrateur|Mila le regarde.
+narrateur|Son ventre se serre.
+narrateur|Ses mains restent sur ses genoux.
+enfant-f|Je suis jalouse.
+maman|Je t'écoute.
+papa|Jaloux, c'est cette envie.
+maman|On peut le dire.
+narrateur|Mila va près de Raphaël.
+enfant-f|Je voudrais demander un tour.
+enfant-m|Encore deux pièces.
+maman|On attend la réponse.
+narrateur|Mila attend.
+narrateur|Les mains restent sur ses genoux.
+narrateur|Elle compte tout bas.
+narrateur|Une pièce. Encore une pièce.
+narrateur|Raphaël pose une pièce.
+narrateur|Puis une autre.
+narrateur|Le vert rejoint le vert.
+enfant-m|C'est ton tour.
+narrateur|Raphaël passe une pièce.
+narrateur|Mila a son tour.
+enfant-f|Merci, Raphaël.
+maman|Tu as demandé un tour.
+maman|Tu as attendu.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai dit : je suis jalouse.
+papa|Puis tu as demandé.
+narrateur|Le rayon a un peu bougé.
+narrateur|Il touche maintenant une étoile du tapis.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1346,7 +1397,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Iris veut le puzzle. Que fait-elle ?</t>
+          <t>Mila veut le puzzle. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1423,14 +1474,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,7 +1553,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Iris veut le puzzle. Que fait-elle ?</t>
+          <t>narrateur|Mila veut le puzzle.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1582,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Iris Je suis jalouse. Elle a demandé un tour.</t>
+          <t>Mila a nommé : jalouse. Elle a demandé un tour. Elle a attendu. Je suis jalouse. J'ai demandé un tour. Oui. Tu as attendu deux pièces. Bravo. C'est du bon travail. Après, je redemande ? On demande. On attend. Les mains sur les genoux. C'est le bon geste. Le plateau de bois est encore tiède. Une pièce ronde attend au bord. Jaloux, on le dit. Puis on demande un tour. Le couvercle reste penché contre le canapé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1591,14 +1643,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1670,8 +1722,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Iris
-enfant-f|Je suis jalouse. Elle a demandé un tour.</t>
+          <t>narrateur|Mila a nommé : jalouse.
+narrateur|Elle a demandé un tour.
+narrateur|Elle a attendu.
+enfant-f|Je suis jalouse.
+enfant-f|J'ai demandé un tour.
+maman|Oui. Tu as attendu deux pièces.
+papa|Bravo. C'est du bon travail.
+enfant-m|Après, je redemande ?
+maman|On demande. On attend.
+enfant-f|Les mains sur les genoux.
+papa|C'est le bon geste.
+narrateur|Le plateau de bois est encore tiède.
+narrateur|Une pièce ronde attend au bord.
+maman|Jaloux, on le dit.
+enfant-f|Puis on demande un tour.
+narrateur|Le couvercle reste penché contre le canapé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1699,7 +1765,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range la boîte. Iris pose une dernière pièce.</t>
+          <t>Maman range la boîte. Mila pose une dernière pièce. On met le couvercle, Mila ? Oui, papa. Merci d'avoir demandé, Mila. Le puzzle est presque fini. Vous avez attendu, tous les deux. J'ai eu mon tour. On peut plier le plateau. Mila touche une étoile du tapis. Le tissu est un peu rêche. Le rayon s'en va, tout doux. Il était jaune. Comme une petite lampe, sur le sol. La boîte se ferme avec un clic.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1760,14 +1826,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1835,7 +1901,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range la boîte. Iris pose une dernière pièce.</t>
+          <t>narrateur|Maman range la boîte.
+narrateur|Mila pose une dernière pièce.
+papa|On met le couvercle, Mila ?
+enfant-f|Oui, papa.
+maman|Merci d'avoir demandé, Mila.
+enfant-m|Le puzzle est presque fini.
+papa|Vous avez attendu, tous les deux.
+enfant-f|J'ai eu mon tour.
+maman|On peut plier le plateau.
+narrateur|Mila touche une étoile du tapis.
+narrateur|Le tissu est un peu rêche.
+papa|Le rayon s'en va, tout doux.
+enfant-f|Il était jaune.
+maman|Comme une petite lampe, sur le sol.
+narrateur|La boîte se ferme avec un clic.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1863,7 +1943,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais jalouse. J'ai demandé un tour. Tu as attendu. Bravo. Le puzzle est dans sa boîte. Le tapis garde ses étoiles. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1924,14 +2004,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2003,7 +2083,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'étais jalouse. J'ai demandé un tour.
+maman|Tu as attendu. Bravo.
+papa|Le puzzle est dans sa boîte.
+narrateur|Le tapis garde ses étoiles.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2025,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2063,6 +2147,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le rideau laisse un rayon jaune. Le rayon tombe sur le tapis. Le tapis a des étoiles grises. Un couvercle de boîte est penché. Il s'appuie contre le canapé. Les pièces du puzzle sont dans un plateau. Le bois du plateau est tiède. Une chaussette attend sur le bras du canapé. Ça sent le linge propre, un peu. Je plie le linge, Mila. Raphaël a déjà commencé le puzzle. Le rayon est chaud, maman. Oui. Il caresse le tapis. Les étoiles du tapis brillent un peu. En ce moment, Raphaël tient le grand puzzle. Une pièce verte est entre ses doigts. Mila le regarde. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jalouse. Je t'écoute. Jaloux, c'est cette envie. On peut le dire. Mila va près de Raphaël. Je voudrais demander un tour. Encore deux pièces. On attend la réponse. Mila attend. Les mains restent sur ses genoux. Elle compte tout bas. Une pièce. Encore une pièce. Raphaël pose une pièce. Puis une autre. Le vert rejoint le vert. C'est ton tour. Raphaël passe une pièce. Mila a son tour. Merci, Raphaël. Tu as demandé un tour. Tu as attendu. Bravo, Mila. Tu as fait du bon travail. J'ai dit : je suis jalouse. Puis tu as demandé. Le rayon a un peu bougé. Il touche maintenant une étoile du tapis.</t>
+          <t>Le rideau laisse un rayon jaune. Le rayon tombe sur le tapis. Le tapis a des étoiles grises. Un couvercle de boîte est penché. Il s'appuie contre le canapé. Les pièces du puzzle sont dans un plateau. Le bois du plateau est tiède. Une chaussette attend sur le bras du canapé. Ça sent le linge propre, un peu. Je plie le linge, Mila. Raphaël a déjà commencé le puzzle. Le rayon est chaud, maman. Oui. Il caresse le tapis. Les étoiles du tapis brillent un peu. En ce moment, Raphaël tient le grand puzzle. Une pièce verte est entre ses doigts. Mila le regarde. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jalouse. Je t'écoute. Jaloux, c'est cette envie. On peut le dire. Mila va près de Raphaël. Je voudrais demander un tour. Encore deux pièces. On attend la réponse. Mila attend. Les mains restent sur ses genoux. Elle compte tout bas. Une pièce. Encore une pièce. Raphaël pose une pièce. Puis une autre. Le vert rejoint le vert. C'est ton tour. Raphaël passe une pièce. Mila a son tour. Merci, Raphaël. Tu as demandé un tour. Tu as attendu. Bravo, Mila. J'ai dit : je suis jalouse. Puis tu as demandé. Le rayon a un peu bougé. Il touche maintenant une étoile du tapis.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Iris est dans le salon avec maman. Tom tient le grand puzzle. Iris le regarde. Son ventre se serre. Elle dit : je suis jalouse. &lt;emphasis level="moderate"&gt;jaloux&lt;/emphasis&gt;, c'est cette envie. Maman écoute. Iris va près de Tom. Elle dit : je voudrais demander un tour. Tom dit : encore deux pièces. Iris attend. Les mains restent sur ses genoux. Puis Tom passe une pièce. Iris a son tour. Maman dit : tu as demandé un tour. Tu as attendu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rideau laisse un rayon jaune. Le rayon tombe sur le tapis. Le tapis a des étoiles grises. Un couvercle de boîte est penché. Il s'appuie contre le canapé. Les pièces du puzzle sont dans un plateau. Le bois du plateau est tiède. Une chaussette attend sur le bras du canapé. Ça sent le linge propre, un peu. Je plie le linge, Mila. Raphaël a déjà commencé le puzzle. Le rayon est chaud, maman. Oui. Il caresse le tapis. Les étoiles du tapis brillent un peu. En ce moment, Raphaël tient le grand puzzle. Une pièce verte est entre ses doigts. Mila le regarde. Son ventre se serre. Ses mains restent sur ses genoux. Je suis jalouse. Je t'écoute. Jaloux, c'est cette envie. On peut le dire. Mila va près de Raphaël. Je voudrais demander un tour. Encore deux pièces. On attend la réponse. Mila attend. Les mains restent sur ses genoux. Elle compte tout bas. Une pièce. Encore une pièce. Raphaël pose une pièce. Puis une autre. Le vert rejoint le vert. C'est ton tour. Raphaël passe une pièce. Mila a son tour. Merci, Raphaël. Tu as demandé un tour. Tu as attendu. Bravo, Mila. J'ai dit : je suis jalouse. Puis tu as demandé. Le rayon a un peu bougé. Il touche maintenant une étoile du tapis.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1365,14 +1365,12 @@
 maman|Tu as demandé un tour.
 maman|Tu as attendu.
 papa|Bravo, Mila.
-papa|Tu as fait du bon travail.
 enfant-f|J'ai dit : je suis jalouse.
 papa|Puis tu as demandé.
 narrateur|Le rayon a un peu bougé.
 narrateur|Il touche maintenant une étoile du tapis.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1402,7 +1400,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Iris veut le puzzle. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila veut le puzzle. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1557,7 +1555,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1582,12 +1579,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mila a nommé : jalouse. Elle a demandé un tour. Elle a attendu. Je suis jalouse. J'ai demandé un tour. Oui. Tu as attendu deux pièces. Bravo. C'est du bon travail. Après, je redemande ? On demande. On attend. Les mains sur les genoux. C'est le bon geste. Le plateau de bois est encore tiède. Une pièce ronde attend au bord. Jaloux, on le dit. Puis on demande un tour. Le couvercle reste penché contre le canapé.</t>
+          <t>Mila a nommé : jalouse. Elle a demandé un tour. Elle a attendu. Je suis jalouse. J'ai demandé un tour. Oui. Tu as attendu deux pièces. Après, je redemande ? On demande. On attend. Les mains sur les genoux. C'est le bon geste. Le plateau de bois est encore tiède. Une pièce ronde attend au bord. Jaloux, on le dit. Puis on demande un tour. Le couvercle reste penché contre le canapé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Iris a dit : je suis jalouse. Elle a demandé un tour.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a nommé : jalouse. Elle a demandé un tour. Elle a attendu. Je suis jalouse. J'ai demandé un tour. Oui. Tu as attendu deux pièces. Après, je redemande ? On demande. On attend. Les mains sur les genoux. C'est le bon geste. Le plateau de bois est encore tiède. Une pièce ronde attend au bord. Jaloux, on le dit. Puis on demande un tour. Le couvercle reste penché contre le canapé.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1728,7 +1725,6 @@
 enfant-f|Je suis jalouse.
 enfant-f|J'ai demandé un tour.
 maman|Oui. Tu as attendu deux pièces.
-papa|Bravo. C'est du bon travail.
 enfant-m|Après, je redemande ?
 maman|On demande. On attend.
 enfant-f|Les mains sur les genoux.
@@ -1740,7 +1736,6 @@
 narrateur|Le couvercle reste penché contre le canapé.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1770,7 +1765,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range la boîte. Iris pose une dernière pièce.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman range la boîte. Mila pose une dernière pièce. On met le couvercle, Mila ? Oui, papa. Merci d'avoir demandé, Mila. Le puzzle est presque fini. Vous avez attendu, tous les deux. J'ai eu mon tour. On peut plier le plateau. Mila touche une étoile du tapis. Le tissu est un peu rêche. Le rayon s'en va, tout doux. Il était jaune. Comme une petite lampe, sur le sol. La boîte se ferme avec un clic.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1918,7 +1913,6 @@
 narrateur|La boîte se ferme avec un clic.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1943,12 +1937,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais jalouse. J'ai demandé un tour. Tu as attendu. Bravo. Le puzzle est dans sa boîte. Le tapis garde ses étoiles. L'histoire est finie.</t>
+          <t>J'étais jalouse. J'ai demandé un tour. Tu as attendu. Bravo. Le puzzle est dans sa boîte. Le tapis garde ses étoiles.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais jalouse. J'ai demandé un tour. Tu as attendu. Bravo. Le puzzle est dans sa boîte. Le tapis garde ses étoiles.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2086,11 +2080,9 @@
           <t>enfant-f|J'étais jalouse. J'ai demandé un tour.
 maman|Tu as attendu. Bravo.
 papa|Le puzzle est dans sa boîte.
-narrateur|Le tapis garde ses étoiles.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le tapis garde ses étoiles.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2109,7 +2101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2154,6 +2146,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-02.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Iris, Tom, maman</t>
+          <t>Mila, Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
